--- a/Templates.xlsx
+++ b/Templates.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pcus1-my.sharepoint.com/personal/lp31801_america_gds_panasonic_com/Documents/Documents/LoganPalmer - Personal/HelpfulEngrThings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\logan\Desktop\HelpfulEngrThings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC104855791F59085ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AE886D-3794-4567-A780-B048C6FE5198}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C03B33A-2E27-4B02-A267-651A803C9784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BoltCalculator" sheetId="5" r:id="rId1"/>
     <sheet name="Metric Bolt Data 4 bolt calc" sheetId="4" r:id="rId2"/>
     <sheet name="BOM TEMPLATE" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -466,9 +462,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -498,9 +491,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="48" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -519,9 +509,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -529,6 +516,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -647,373 +643,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Ws"/>
-      <sheetName val="Meeting Rooms"/>
-      <sheetName val="BOM TEMPLATE"/>
-      <sheetName val="pType shops"/>
-      <sheetName val="BoltCalculator"/>
-      <sheetName val="Supermarket Pending"/>
-      <sheetName val="Technical Writing Pending"/>
-      <sheetName val="Open Projects"/>
-      <sheetName val="Pretty Schedule Template"/>
-      <sheetName val="OT tracker"/>
-      <sheetName val="Metric Bolt Data 4 bolt calc"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Thread Size</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Minor Diameter (mm)</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Thread Pitch (mm)</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>M1</v>
-          </cell>
-          <cell r="C4">
-            <v>0.72899999999999998</v>
-          </cell>
-          <cell r="D4">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>M1.1</v>
-          </cell>
-          <cell r="C5">
-            <v>0.82899999999999996</v>
-          </cell>
-          <cell r="D5">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>M1.2</v>
-          </cell>
-          <cell r="C6">
-            <v>0.92900000000000005</v>
-          </cell>
-          <cell r="D6">
-            <v>0.25</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>M1.4</v>
-          </cell>
-          <cell r="C7">
-            <v>1.075</v>
-          </cell>
-          <cell r="D7">
-            <v>0.3</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>M1.6</v>
-          </cell>
-          <cell r="C8">
-            <v>1.2210000000000001</v>
-          </cell>
-          <cell r="D8">
-            <v>0.35</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>M1.8</v>
-          </cell>
-          <cell r="C9">
-            <v>1.421</v>
-          </cell>
-          <cell r="D9">
-            <v>0.35</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>M2</v>
-          </cell>
-          <cell r="C10">
-            <v>1.5669999999999999</v>
-          </cell>
-          <cell r="D10">
-            <v>0.4</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>M2.2</v>
-          </cell>
-          <cell r="C11">
-            <v>1.7130000000000001</v>
-          </cell>
-          <cell r="D11">
-            <v>0.45</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>M2.5</v>
-          </cell>
-          <cell r="C12">
-            <v>2.0129999999999999</v>
-          </cell>
-          <cell r="D12">
-            <v>0.45</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>M3</v>
-          </cell>
-          <cell r="C13">
-            <v>2.4590000000000001</v>
-          </cell>
-          <cell r="D13">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>M3.5</v>
-          </cell>
-          <cell r="C14">
-            <v>2.85</v>
-          </cell>
-          <cell r="D14">
-            <v>0.6</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>M4</v>
-          </cell>
-          <cell r="C15">
-            <v>3.242</v>
-          </cell>
-          <cell r="D15">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>M4.5</v>
-          </cell>
-          <cell r="C16">
-            <v>3.6880000000000002</v>
-          </cell>
-          <cell r="D16">
-            <v>0.75</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>M5</v>
-          </cell>
-          <cell r="C17">
-            <v>4.1340000000000003</v>
-          </cell>
-          <cell r="D17">
-            <v>0.8</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>M6</v>
-          </cell>
-          <cell r="C18">
-            <v>4.9169999999999998</v>
-          </cell>
-          <cell r="D18">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>M7</v>
-          </cell>
-          <cell r="C19">
-            <v>5.9169999999999998</v>
-          </cell>
-          <cell r="D19">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>M8</v>
-          </cell>
-          <cell r="C20">
-            <v>6.6470000000000002</v>
-          </cell>
-          <cell r="D20">
-            <v>1.25</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>M9</v>
-          </cell>
-          <cell r="C21">
-            <v>7.6470000000000002</v>
-          </cell>
-          <cell r="D21">
-            <v>1.25</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>M10</v>
-          </cell>
-          <cell r="C22">
-            <v>8.3759999999999994</v>
-          </cell>
-          <cell r="D22">
-            <v>1.5</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>M11</v>
-          </cell>
-          <cell r="C23">
-            <v>9.3759999999999994</v>
-          </cell>
-          <cell r="D23">
-            <v>1.5</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>M12</v>
-          </cell>
-          <cell r="C24">
-            <v>10.106</v>
-          </cell>
-          <cell r="D24">
-            <v>1.75</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>M14</v>
-          </cell>
-          <cell r="C25">
-            <v>11.835000000000001</v>
-          </cell>
-          <cell r="D25">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>M16</v>
-          </cell>
-          <cell r="C26">
-            <v>13.835000000000001</v>
-          </cell>
-          <cell r="D26">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>M18</v>
-          </cell>
-          <cell r="C27">
-            <v>15.394</v>
-          </cell>
-          <cell r="D27">
-            <v>2.5</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>M20</v>
-          </cell>
-          <cell r="C28">
-            <v>17.294</v>
-          </cell>
-          <cell r="D28">
-            <v>2.5</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>M22</v>
-          </cell>
-          <cell r="C29">
-            <v>19.294</v>
-          </cell>
-          <cell r="D29">
-            <v>2.5</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>M24</v>
-          </cell>
-          <cell r="C30">
-            <v>20.751999999999999</v>
-          </cell>
-          <cell r="D30">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>M27</v>
-          </cell>
-          <cell r="C31">
-            <v>23.751999999999999</v>
-          </cell>
-          <cell r="D31">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>M30</v>
-          </cell>
-          <cell r="C32">
-            <v>26.210999999999999</v>
-          </cell>
-          <cell r="D32">
-            <v>3.5</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1282,318 +911,318 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="49.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>600000000</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="M3" s="9" t="s">
+      <c r="D3" s="10"/>
+      <c r="M3" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>0.75</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="F5" s="9" t="s">
+      <c r="B5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="15">
-        <f>_xlfn.XLOOKUP(B5,'[1]Metric Bolt Data 4 bolt calc'!A:A,'[1]Metric Bolt Data 4 bolt calc'!C:C,"NOT FOUND")/1000</f>
-        <v>8.3759999999999998E-3</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="B6" s="14">
+        <f>_xlfn.XLOOKUP(B5,'Metric Bolt Data 4 bolt calc'!A:A,'Metric Bolt Data 4 bolt calc'!C:C,"NOT FOUND")/1000</f>
+        <v>4.9169999999999995E-3</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="15">
-        <f>_xlfn.XLOOKUP(B5,'[1]Metric Bolt Data 4 bolt calc'!A:A,'[1]Metric Bolt Data 4 bolt calc'!D:D,"NOT FOUND")/1000</f>
-        <v>1.5E-3</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="B7" s="14">
+        <f>_xlfn.XLOOKUP(B5,'Metric Bolt Data 4 bolt calc'!A:A,'Metric Bolt Data 4 bolt calc'!D:D,"NOT FOUND")/1000</f>
+        <v>1E-3</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>0.15</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <v>0.15</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
+      <c r="B11" s="16"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
+      <c r="B12" s="16"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="17">
         <f>(PI()*B6^2)/4</f>
-        <v>5.5101474259184218E-5</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="11"/>
+        <v>1.8988484217263967E-5</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <f>B3*B4*B15</f>
-        <v>24795.663416632899</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="11"/>
+        <v>8544.8178977687858</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="18">
         <f>AVERAGE(B5:B6)</f>
-        <v>8.3759999999999998E-3</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+        <v>4.9169999999999995E-3</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>30</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <f>(B7+PI()*B9*B17*_xlfn.SEC(RADIANS(B18)))/(PI()*B17-B9*B7*_xlfn.SEC(RADIANS(B18)))</f>
-        <v>0.23250460382720362</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+        <v>0.24063991089942352</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <f>B10*B8/2</f>
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="21">
         <f>(B16*B17*B19/2)+(B16*B20)</f>
-        <v>35.302312043824053</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+        <v>8.9003952928939611</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="21">
         <f>B21*8.85075</f>
-        <v>312.45193832187573</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+        <v>78.775173638581222</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="21">
         <f>B21*0.7376</f>
-        <v>26.038985363524624</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+        <v>6.5649315680385865</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="19">
         <f>B3*B15</f>
-        <v>33060.884555510529</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+        <v>11393.09053035838</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="19">
         <f>B3*B4*B15</f>
-        <v>24795.663416632899</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
+        <v>8544.8178977687858</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="19">
         <f>B28-B29</f>
-        <v>8265.2211388776304</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+        <v>2848.2726325895947</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1623,733 +1252,733 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="16" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="23" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="22" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="24">
         <v>1</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="24">
         <v>0.72899999999999998</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="24">
         <v>0.25</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="24">
         <v>0.83799999999999997</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="24">
         <v>0.75</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="24">
         <v>1.3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="25">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="25">
         <v>0.82899999999999996</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="25">
         <v>0.25</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="25">
         <v>0.93799999999999994</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="25">
         <v>0.85</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="25">
         <v>1.4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="24">
         <v>1.2</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="24">
         <v>0.92900000000000005</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="24">
         <v>0.25</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="24">
         <v>1.038</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="24">
         <v>0.95</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="24">
         <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="25">
         <v>1.4</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>1.075</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="25">
         <v>0.3</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="25">
         <v>1.2050000000000001</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="25">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="25">
         <v>1.8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="24">
         <v>1.6</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="24">
         <v>1.2210000000000001</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="24">
         <v>0.35</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="24">
         <v>1.373</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="24">
         <v>1.25</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="24">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="25">
         <v>1.8</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="25">
         <v>1.421</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="25">
         <v>0.35</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="25">
         <v>1.573</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="25">
         <v>1.45</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="25">
         <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="24">
         <v>2</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="24">
         <v>1.5669999999999999</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="24">
         <v>0.4</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="24">
         <v>1.74</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="24">
         <v>1.6</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="24">
         <v>2.6</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="25">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="25">
         <v>1.7130000000000001</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="25">
         <v>0.45</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="25">
         <v>1.9079999999999999</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="25">
         <v>1.75</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="25">
         <v>2.9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="24">
         <v>2.5</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="24">
         <v>2.0129999999999999</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="24">
         <v>0.45</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="24">
         <v>2.2080000000000002</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="24">
         <v>2.0499999999999998</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="24">
         <v>3.1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="25">
         <v>3</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="25">
         <v>2.4590000000000001</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="25">
         <v>0.5</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="25">
         <v>2.6749999999999998</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="25">
         <v>2.5</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="25">
         <v>3.6</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="24">
         <v>3.5</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="24">
         <v>2.85</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="24">
         <v>0.6</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="24">
         <v>3.11</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="24">
         <v>2.9</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="24">
         <v>4.2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="25">
         <v>4</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="25">
         <v>3.242</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="25">
         <v>0.7</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="25">
         <v>3.5449999999999999</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="25">
         <v>3.3</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="25">
         <v>4.8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="24">
         <v>4.5</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="24">
         <v>3.6880000000000002</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="24">
         <v>0.75</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="24">
         <v>4.0129999999999999</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="24">
         <v>3.8</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="24">
         <v>5.3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="25">
         <v>5</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="25">
         <v>4.1340000000000003</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="25">
         <v>0.8</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="25">
         <v>4.4800000000000004</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="25">
         <v>4.2</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="25">
         <v>5.8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="24">
         <v>6</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="24">
         <v>4.9169999999999998</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="24">
         <v>1</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="24">
         <v>5.35</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="24">
         <v>5</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="24">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="25">
         <v>7</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="25">
         <v>5.9169999999999998</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="25">
         <v>1</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="25">
         <v>6.35</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="25">
         <v>6</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="25">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="24">
         <v>8</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="24">
         <v>6.6470000000000002</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="24">
         <v>1.25</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="24">
         <v>7.1879999999999997</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="24">
         <v>6.8</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="24">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="25">
         <v>9</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="25">
         <v>7.6470000000000002</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="25">
         <v>1.25</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="25">
         <v>8.1880000000000006</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="25">
         <v>7.8</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="25">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="24">
         <v>10</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="24">
         <v>8.3759999999999994</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="24">
         <v>1.5</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="24">
         <v>9.0259999999999998</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="24">
         <v>8.5</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="24">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="25">
         <v>11</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="25">
         <v>9.3759999999999994</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="25">
         <v>1.5</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="25">
         <v>10.026</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="25">
         <v>9.5</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="25">
         <v>13.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="24">
         <v>12</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="24">
         <v>10.106</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="24">
         <v>1.75</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="24">
         <v>10.863</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="24">
         <v>10.199999999999999</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="24">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="25">
         <v>14</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="25">
         <v>11.835000000000001</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="25">
         <v>2</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="25">
         <v>12.701000000000001</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="25">
         <v>12</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="25">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="24">
         <v>16</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="24">
         <v>13.835000000000001</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="24">
         <v>2</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="24">
         <v>14.701000000000001</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="24">
         <v>14</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="24">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="25">
         <v>18</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="25">
         <v>15.394</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="25">
         <v>2.5</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="25">
         <v>16.376000000000001</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="25">
         <v>15.5</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="25">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="24">
         <v>20</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="24">
         <v>17.294</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="24">
         <v>2.5</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="24">
         <v>18.376000000000001</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="24">
         <v>17.5</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="24">
         <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="25">
         <v>22</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="25">
         <v>19.294</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="25">
         <v>2.5</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="25">
         <v>20.376000000000001</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="25">
         <v>19.5</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="25">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="24">
         <v>24</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="24">
         <v>20.751999999999999</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="24">
         <v>3</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="24">
         <v>22.050999999999998</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="24">
         <v>21</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="24">
         <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="25">
         <v>27</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="25">
         <v>23.751999999999999</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="25">
         <v>3</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="25">
         <v>25.050999999999998</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="25">
         <v>24</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="25">
         <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="24">
         <v>30</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="24">
         <v>26.210999999999999</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="24">
         <v>3.5</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="24">
         <v>27.727</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="24">
         <v>26.5</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="24">
         <v>35</v>
       </c>
     </row>
@@ -8760,13 +8389,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>